--- a/artfynd/A 61205-2024 artfynd.xlsx
+++ b/artfynd/A 61205-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4820607</v>
+        <v>3937006</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405641.709816226</v>
+        <v>405637</v>
       </c>
       <c r="R2" t="n">
-        <v>6666376.205613459</v>
+        <v>6666295</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,14 @@
           <t>2012-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3937006</v>
+        <v>4241319</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405636.6274883137</v>
+        <v>405642</v>
       </c>
       <c r="R3" t="n">
-        <v>6666295.067379865</v>
+        <v>6666376</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,24 +850,9 @@
           <t>2012-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4241319</v>
+        <v>4887957</v>
       </c>
       <c r="B4" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,16 +895,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222002</v>
+        <v>222395</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405641.709816226</v>
+        <v>405625</v>
       </c>
       <c r="R4" t="n">
-        <v>6666376.205613459</v>
+        <v>6666485</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,19 +952,9 @@
           <t>2012-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4887957</v>
+        <v>4820607</v>
       </c>
       <c r="B5" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222395</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1071,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405624.5265691398</v>
+        <v>405642</v>
       </c>
       <c r="R5" t="n">
-        <v>6666484.836937422</v>
+        <v>6666376</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,19 +1054,9 @@
           <t>2012-06-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-06-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,6 +1085,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5286973</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mjögsjöhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>405624</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666115</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-06-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-06-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskogsbryn</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Crister Albinsson, Jan Teodorsson, Per Larsson, Stina Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61205-2024 artfynd.xlsx
+++ b/artfynd/A 61205-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3937006</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4241319</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4887957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4820607</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,8 +1212,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5286973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>